--- a/templates/Directory-0.xlsx
+++ b/templates/Directory-0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Downloads\_sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F69B0D-DB77-4DA4-9A2F-63227FC03892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD431F4-644F-42FC-9976-6E8922F18E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Directory of Participants" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>Directory of Participants</t>
   </si>
@@ -125,13 +125,7 @@
     <t> PREPARED BY:</t>
   </si>
   <si>
-    <t>Training Assistant</t>
-  </si>
-  <si>
     <t>NOTED BY:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiing Manager </t>
   </si>
   <si>
     <t>LIST OF TRAININGS CONDUCTED</t>
@@ -209,607 +203,16 @@
     <t>Date Issued</t>
   </si>
   <si>
-    <t>Online</t>
-  </si>
-  <si>
     <t>[INSERT OSNET/STO  HEADER WITH LOGO HERE]</t>
-  </si>
-  <si>
-    <t>Online Training</t>
   </si>
   <si>
     <t>PETROSPHERE INCORPORATED</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>Training Facilitator</t>
   </si>
   <si>
-    <t xml:space="preserve">Online Training </t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>REGION 4-B</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>MICHELLE M. SACLET</t>
-  </si>
-  <si>
-    <t>JEFFREY C. GEALON</t>
-  </si>
-  <si>
-    <t>May 31-June 4, 2021</t>
-  </si>
-  <si>
-    <t>San Pedro</t>
-  </si>
-  <si>
-    <t>Puerto Princesa City</t>
-  </si>
-  <si>
-    <t>Palawan</t>
-  </si>
-  <si>
-    <t>Region 4-B</t>
-  </si>
-  <si>
-    <t>Michelle M. Saclet</t>
-  </si>
-  <si>
-    <t>OCAMPO</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>JR</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Caloocan</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>09756784538</t>
-  </si>
-  <si>
-    <t>DEMPSEY</t>
-  </si>
-  <si>
-    <t>DJ</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001841</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001842</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001843</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001844</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001845</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001846</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001847</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001848</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001849</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001850</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001851</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001852</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001853</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001854</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001855</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001856</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001857</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001858</t>
-  </si>
-  <si>
-    <t>PANES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRINCE </t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>JEANLY</t>
-  </si>
-  <si>
-    <t>MATUGAS</t>
-  </si>
-  <si>
-    <t>MICO ALUEL</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>COLONIA</t>
-  </si>
-  <si>
-    <t>JOHN ERIC</t>
-  </si>
-  <si>
-    <t>MIKE JAYSON</t>
-  </si>
-  <si>
-    <t>MAQUIDANG</t>
-  </si>
-  <si>
-    <t>ARQUE</t>
-  </si>
-  <si>
-    <t>PIM ISMAEL</t>
-  </si>
-  <si>
-    <t>ALIB</t>
-  </si>
-  <si>
-    <t>ALYSSA MAE</t>
-  </si>
-  <si>
-    <t>DELA TORRE</t>
-  </si>
-  <si>
-    <t>JOHANN DARNELY</t>
-  </si>
-  <si>
-    <t>RECOCO</t>
-  </si>
-  <si>
-    <t>GWEN ARIANNE</t>
-  </si>
-  <si>
-    <t>MINO</t>
-  </si>
-  <si>
-    <t>REGINA DANIELLE</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>JOSHUA</t>
-  </si>
-  <si>
-    <t>PANDI</t>
-  </si>
-  <si>
-    <t>AL WAHID</t>
-  </si>
-  <si>
-    <t>EBING</t>
-  </si>
-  <si>
-    <t>AMANODIN</t>
-  </si>
-  <si>
-    <t>MOHAMMAD WALID</t>
-  </si>
-  <si>
-    <t>BAIDDIN</t>
-  </si>
-  <si>
-    <t>CERCHEA NIVIA</t>
-  </si>
-  <si>
-    <t>JOHN ARGIE</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>DAYAP</t>
-  </si>
-  <si>
-    <t>EMERY</t>
-  </si>
-  <si>
-    <t>MAGHANOY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDREW GEM </t>
-  </si>
-  <si>
-    <t>GUANZON</t>
-  </si>
-  <si>
-    <t>CARL JOSEPH</t>
-  </si>
-  <si>
-    <t>MACARIOLA</t>
-  </si>
-  <si>
-    <t>MARY ANTONNETTE</t>
-  </si>
-  <si>
-    <t>JESSIE</t>
-  </si>
-  <si>
-    <t>LUCHANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARK ANTHONY </t>
-  </si>
-  <si>
-    <t>SAYARI</t>
-  </si>
-  <si>
-    <t>JULHARI</t>
-  </si>
-  <si>
-    <t>SABAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MA. ELAINE </t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>ROTAIRO</t>
-  </si>
-  <si>
-    <t>SAM RIAN</t>
-  </si>
-  <si>
-    <t>DENOSTA</t>
-  </si>
-  <si>
-    <t>ARNEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PADILLA </t>
-  </si>
-  <si>
-    <t>CARMELA JOICE</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>PETROSPHERE INC.</t>
-  </si>
-  <si>
-    <t>HSEEQ/TRAINING OFFICER</t>
-  </si>
-  <si>
-    <t>SERVICES</t>
-  </si>
-  <si>
-    <t>cjp@petrosphere.com.ph</t>
-  </si>
-  <si>
-    <t>CJN.Padilla18@outlook.com</t>
-  </si>
-  <si>
-    <t>09450907811</t>
-  </si>
-  <si>
-    <t>048 717 1288</t>
-  </si>
-  <si>
-    <t>carlguanz@gmail.com</t>
-  </si>
-  <si>
-    <t>09451283469</t>
-  </si>
-  <si>
-    <t>N?A</t>
-  </si>
-  <si>
-    <t>maelainesabat065@gmail.com</t>
-  </si>
-  <si>
-    <t>09125418136</t>
-  </si>
-  <si>
-    <t>castillo.jessie2399@gmail.com</t>
-  </si>
-  <si>
-    <t>09158514519</t>
-  </si>
-  <si>
-    <t>minoregina14@gmail.com</t>
-  </si>
-  <si>
-    <t>09959481970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jsayari10@gmail.com </t>
-  </si>
-  <si>
-    <t>09555012175</t>
-  </si>
-  <si>
-    <t>luchanamark@yhoo.com</t>
-  </si>
-  <si>
-    <t>09772850867</t>
-  </si>
-  <si>
-    <t>alyssaalib09@gmail.com</t>
-  </si>
-  <si>
-    <t>09397520447</t>
-  </si>
-  <si>
-    <t>arquepim17@gmail.com</t>
-  </si>
-  <si>
-    <t>09204967363</t>
-  </si>
-  <si>
-    <t>nnahoj26@gmail.com</t>
-  </si>
-  <si>
-    <t>09298192373</t>
-  </si>
-  <si>
-    <t>newgarianne0919@gmail.com</t>
-  </si>
-  <si>
-    <t>09166266316</t>
-  </si>
-  <si>
-    <t>princepanes93@gmail.com</t>
-  </si>
-  <si>
-    <t>09959845472</t>
-  </si>
-  <si>
-    <t>venturajean21@gmail.com</t>
-  </si>
-  <si>
-    <t>09683794867</t>
-  </si>
-  <si>
-    <t>ENGIERES</t>
-  </si>
-  <si>
-    <t>engieresj@gmail.com</t>
-  </si>
-  <si>
-    <t>09981738454</t>
-  </si>
-  <si>
-    <t>duckmcdonald70@gmail.com</t>
-  </si>
-  <si>
-    <t>09461439230</t>
-  </si>
-  <si>
-    <t>cbaiddin@gmail.com</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>09366882463</t>
-  </si>
-  <si>
-    <t>mamacariola12@gmail.com</t>
-  </si>
-  <si>
-    <t>09076690000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTOPACE </t>
-  </si>
-  <si>
-    <t>BERTRAM</t>
-  </si>
-  <si>
-    <t>DENEESE KYLA</t>
-  </si>
-  <si>
-    <t>bertramestopace@gmail.com</t>
-  </si>
-  <si>
-    <t>09567587313</t>
-  </si>
-  <si>
-    <t>maquidangmikejayson2@gmail.com</t>
-  </si>
-  <si>
-    <t>09754532750</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001859</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001860</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001861</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001862</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001863</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEBIDO </t>
-  </si>
-  <si>
-    <t>DEXTER</t>
-  </si>
-  <si>
-    <t>dextersebido18@gmail.com</t>
-  </si>
-  <si>
-    <t>09996938267</t>
-  </si>
-  <si>
-    <t>deneesekylatebing@gmail.com</t>
-  </si>
-  <si>
-    <t>09260062257</t>
-  </si>
-  <si>
-    <t>mohammadwalidamanodin@gmail.com</t>
-  </si>
-  <si>
-    <t>09054675001</t>
-  </si>
-  <si>
-    <t>alpandi1989@gmail.com</t>
-  </si>
-  <si>
-    <t>09998627273</t>
-  </si>
-  <si>
-    <t>mico.aluel@gmail.com</t>
-  </si>
-  <si>
-    <t>09085837669</t>
-  </si>
-  <si>
-    <t>Greatwest Industries Gases</t>
-  </si>
-  <si>
-    <t>Liason Officer</t>
-  </si>
-  <si>
-    <t>Industrial</t>
-  </si>
-  <si>
-    <t>contact@greatwestgases.com</t>
-  </si>
-  <si>
-    <t>zhadia_29@yahoo.com</t>
-  </si>
-  <si>
-    <t>09502467755</t>
-  </si>
-  <si>
-    <t>ericcolonia@gmail.com</t>
-  </si>
-  <si>
-    <t>09469655263</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001866</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001867</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001868</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001869</t>
-  </si>
-  <si>
-    <t>PSI-BOSHSO2-001870</t>
-  </si>
-  <si>
-    <t>ocampodempsey@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09154764740 </t>
-  </si>
-  <si>
-    <t>August 16-20, 2021</t>
-  </si>
-  <si>
-    <t>andrew.maghanoy18@gmail.com</t>
-  </si>
-  <si>
-    <t>09474415171</t>
-  </si>
-  <si>
-    <t>BOSH for SO2</t>
-  </si>
-  <si>
-    <t>samrotairoo@gmail.com</t>
-  </si>
-  <si>
-    <t>Citinickel Mines and Development Corporation</t>
-  </si>
-  <si>
-    <t>NARRA , PALAWAN</t>
-  </si>
-  <si>
-    <t>Warehouse/Depo Head</t>
-  </si>
-  <si>
-    <t>Mining</t>
-  </si>
-  <si>
-    <t>cmdctnmpwarehouse@gmail.com</t>
-  </si>
-  <si>
-    <t>arneldenosta85@gmail.com</t>
-  </si>
-  <si>
-    <t>09460719556</t>
-  </si>
-  <si>
-    <t>August 25, 2021</t>
+    <t>Operations Manager</t>
   </si>
 </sst>
 </file>
@@ -1990,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D9" s="89"/>
       <c r="E9" s="89"/>
@@ -2132,1833 +1535,751 @@
       <c r="A15" s="9">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>89</v>
-      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="22">
-        <v>39</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="O15" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="P15" s="76" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q15" s="73" t="s">
-        <v>245</v>
-      </c>
-      <c r="R15" s="22" t="s">
-        <v>62</v>
-      </c>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="22"/>
       <c r="S15"/>
-      <c r="T15" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="U15" s="34">
-        <v>2</v>
-      </c>
+      <c r="T15" s="23"/>
+      <c r="U15" s="34"/>
     </row>
     <row r="16" spans="1:26" s="49" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>2</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>67</v>
-      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
       <c r="F16" s="53"/>
-      <c r="G16" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="53">
-        <v>22</v>
-      </c>
-      <c r="I16" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="K16" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N16" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O16" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="P16" s="68" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q16" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="R16" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="68"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="53"/>
       <c r="S16"/>
-      <c r="T16" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="U16" s="34">
-        <v>2</v>
-      </c>
+      <c r="T16" s="23"/>
+      <c r="U16" s="34"/>
     </row>
     <row r="17" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>3</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>67</v>
-      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="53"/>
-      <c r="G17" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="53">
-        <v>21</v>
-      </c>
-      <c r="I17" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K17" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L17" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O17" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P17" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q17" s="67" t="s">
-        <v>195</v>
-      </c>
-      <c r="R17" s="83" t="s">
-        <v>62</v>
-      </c>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="83"/>
       <c r="S17" s="31"/>
-      <c r="T17" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U17" s="34">
-        <v>2</v>
-      </c>
+      <c r="T17" s="82"/>
+      <c r="U17" s="34"/>
     </row>
     <row r="18" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>4</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>114</v>
-      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
       <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="53">
-        <v>20</v>
-      </c>
-      <c r="I18" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J18" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="K18" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L18" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O18" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="P18" s="68" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q18" s="67" t="s">
-        <v>230</v>
-      </c>
-      <c r="R18" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="54"/>
       <c r="S18"/>
-      <c r="T18" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U18" s="34">
-        <v>2</v>
-      </c>
+      <c r="T18" s="82"/>
+      <c r="U18" s="34"/>
     </row>
     <row r="19" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>5</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>64</v>
-      </c>
+      <c r="B19" s="22"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
       <c r="F19" s="53"/>
-      <c r="G19" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="53">
-        <v>21</v>
-      </c>
-      <c r="I19" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J19" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="K19" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="L19" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M19" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N19" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O19" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="P19" s="68" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q19" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="R19" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="54"/>
       <c r="S19" s="31"/>
-      <c r="T19" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U19" s="34">
-        <v>2</v>
-      </c>
+      <c r="T19" s="82"/>
+      <c r="U19" s="34"/>
     </row>
     <row r="20" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>6</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>82</v>
-      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
       <c r="F20" s="53"/>
-      <c r="G20" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="53">
-        <v>23</v>
-      </c>
-      <c r="I20" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K20" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L20" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O20" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P20" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q20" s="67" t="s">
-        <v>212</v>
-      </c>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="67"/>
       <c r="R20" s="53"/>
       <c r="S20"/>
-      <c r="T20" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U20" s="34">
-        <v>2</v>
-      </c>
+      <c r="T20" s="54"/>
+      <c r="U20" s="34"/>
     </row>
     <row r="21" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>7</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>68</v>
-      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
       <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="53">
-        <v>21</v>
-      </c>
-      <c r="I21" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="K21" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M21" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N21" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O21" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P21" s="68" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q21" s="67" t="s">
-        <v>187</v>
-      </c>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="67"/>
       <c r="R21" s="54"/>
       <c r="S21" s="31"/>
-      <c r="T21" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U21" s="34">
-        <v>2</v>
-      </c>
+      <c r="T21" s="82"/>
+      <c r="U21" s="34"/>
     </row>
     <row r="22" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>8</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>64</v>
-      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
       <c r="F22" s="53"/>
-      <c r="G22" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="53">
-        <v>21</v>
-      </c>
-      <c r="I22" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J22" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K22" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L22" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N22" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O22" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P22" s="77" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q22" s="74" t="s">
-        <v>185</v>
-      </c>
-      <c r="R22" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="77"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="54"/>
       <c r="S22" s="31"/>
-      <c r="T22" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U22" s="34">
-        <v>2</v>
-      </c>
+      <c r="T22" s="82"/>
+      <c r="U22" s="34"/>
     </row>
     <row r="23" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>9</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>80</v>
-      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
       <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="53">
-        <v>21</v>
-      </c>
-      <c r="I23" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="K23" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M23" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N23" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O23" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P23" s="68" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q23" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="R23" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="68"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="54"/>
       <c r="S23" s="31"/>
-      <c r="T23" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U23" s="34">
-        <v>2</v>
-      </c>
+      <c r="T23" s="82"/>
+      <c r="U23" s="34"/>
     </row>
     <row r="24" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>10</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>86</v>
-      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
       <c r="F24" s="53"/>
-      <c r="G24" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="53">
-        <v>21</v>
-      </c>
-      <c r="I24" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J24" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K24" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M24" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="N24" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O24" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P24" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q24" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="R24" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="68"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="54"/>
       <c r="S24" s="34"/>
-      <c r="T24" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U24" s="34">
-        <v>2</v>
-      </c>
+      <c r="T24" s="82"/>
+      <c r="U24" s="34"/>
     </row>
     <row r="25" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>11</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>129</v>
-      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
       <c r="F25" s="53"/>
-      <c r="G25" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="53">
-        <v>22</v>
-      </c>
-      <c r="I25" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K25" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L25" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M25" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N25" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O25" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P25" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q25" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="R25" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="68"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="54"/>
       <c r="S25" s="34"/>
-      <c r="T25" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U25" s="34">
-        <v>2</v>
-      </c>
+      <c r="T25" s="82"/>
+      <c r="U25" s="34"/>
     </row>
     <row r="26" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>12</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>80</v>
-      </c>
+      <c r="B26" s="22"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
       <c r="F26" s="53"/>
-      <c r="G26" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="53">
-        <v>21</v>
-      </c>
-      <c r="I26" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K26" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L26" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M26" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N26" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O26" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P26" s="68" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q26" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="R26" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="68"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="54"/>
       <c r="S26" s="34"/>
-      <c r="T26" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U26" s="34">
-        <v>2</v>
-      </c>
+      <c r="T26" s="82"/>
+      <c r="U26" s="34"/>
     </row>
     <row r="27" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>13</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="53" t="s">
-        <v>80</v>
-      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
       <c r="F27" s="53"/>
-      <c r="G27" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="53">
-        <v>21</v>
-      </c>
-      <c r="I27" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K27" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L27" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M27" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N27" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O27" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P27" s="68" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q27" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="R27" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="68"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="54"/>
       <c r="S27" s="34"/>
-      <c r="T27" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U27" s="34">
-        <v>2</v>
-      </c>
+      <c r="T27" s="82"/>
+      <c r="U27" s="34"/>
     </row>
     <row r="28" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>14</v>
       </c>
-      <c r="B28" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>83</v>
-      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
       <c r="F28" s="53"/>
-      <c r="G28" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="53">
-        <v>21</v>
-      </c>
-      <c r="I28" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K28" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L28" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M28" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N28" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O28" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P28" s="68" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q28" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="R28" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="66"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="54"/>
       <c r="S28" s="34"/>
-      <c r="T28" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U28" s="34">
-        <v>2</v>
-      </c>
+      <c r="T28" s="82"/>
+      <c r="U28" s="34"/>
     </row>
     <row r="29" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>15</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="E29" s="53" t="s">
-        <v>80</v>
-      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
       <c r="F29" s="53"/>
-      <c r="G29" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="53">
-        <v>22</v>
-      </c>
-      <c r="I29" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J29" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K29" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L29" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M29" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N29" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O29" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P29" s="68" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q29" s="67" t="s">
-        <v>210</v>
-      </c>
-      <c r="R29" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="54"/>
       <c r="S29" s="34"/>
-      <c r="T29" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U29" s="34">
-        <v>2</v>
-      </c>
+      <c r="T29" s="82"/>
+      <c r="U29" s="34"/>
     </row>
     <row r="30" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>16</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>64</v>
-      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
       <c r="F30" s="53"/>
-      <c r="G30" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="53">
-        <v>22</v>
-      </c>
-      <c r="I30" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K30" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L30" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M30" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N30" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O30" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P30" s="78" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q30" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="R30" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="78"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="54"/>
       <c r="S30" s="34"/>
-      <c r="T30" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U30" s="34">
-        <v>2</v>
-      </c>
+      <c r="T30" s="82"/>
+      <c r="U30" s="34"/>
     </row>
     <row r="31" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>17</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" s="53" t="s">
-        <v>68</v>
-      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
       <c r="F31" s="53"/>
-      <c r="G31" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="53">
-        <v>21</v>
-      </c>
-      <c r="I31" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J31" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K31" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="L31" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O31" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="P31" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q31" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="R31" s="81" t="s">
-        <v>202</v>
-      </c>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="59"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="68"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="81"/>
       <c r="S31"/>
-      <c r="T31" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U31" s="34">
-        <v>2</v>
-      </c>
+      <c r="T31" s="82"/>
+      <c r="U31" s="34"/>
     </row>
     <row r="32" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>18</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="D32" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>140</v>
-      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
       <c r="F32" s="53"/>
-      <c r="G32" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="53">
-        <v>21</v>
-      </c>
-      <c r="I32" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J32" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K32" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L32" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M32" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N32" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O32" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="P32" s="68" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q32" s="67" t="s">
-        <v>198</v>
-      </c>
-      <c r="R32" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="68"/>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="54"/>
       <c r="S32" s="34"/>
-      <c r="T32" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U32" s="34">
-        <v>2</v>
-      </c>
+      <c r="T32" s="82"/>
+      <c r="U32" s="34"/>
     </row>
     <row r="33" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>19</v>
       </c>
-      <c r="B33" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="C33" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" s="53" t="s">
-        <v>220</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>84</v>
-      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
       <c r="F33" s="53"/>
-      <c r="G33" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="53">
-        <v>21</v>
-      </c>
-      <c r="I33" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J33" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K33" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L33" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M33" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N33" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O33" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P33" s="79" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q33" s="67" t="s">
-        <v>222</v>
-      </c>
-      <c r="R33" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="66"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="54"/>
       <c r="S33" s="34"/>
-      <c r="T33" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U33" s="34">
-        <v>2</v>
-      </c>
+      <c r="T33" s="82"/>
+      <c r="U33" s="34"/>
     </row>
     <row r="34" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>20</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="C34" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>84</v>
-      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
       <c r="F34" s="53"/>
-      <c r="G34" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="53">
-        <v>45</v>
-      </c>
-      <c r="I34" s="59" t="s">
-        <v>231</v>
-      </c>
-      <c r="J34" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="K34" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="L34" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="M34" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="N34" s="53">
-        <v>10</v>
-      </c>
-      <c r="O34" s="72" t="s">
-        <v>234</v>
-      </c>
-      <c r="P34" s="68" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q34" s="67" t="s">
-        <v>236</v>
-      </c>
-      <c r="R34" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="59"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="68"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="54"/>
       <c r="S34" s="34"/>
-      <c r="T34" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U34" s="34">
-        <v>2</v>
-      </c>
+      <c r="T34" s="82"/>
+      <c r="U34" s="34"/>
     </row>
     <row r="35" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>21</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" s="53" t="s">
-        <v>78</v>
-      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
       <c r="F35" s="53"/>
-      <c r="G35" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="53">
-        <v>21</v>
-      </c>
-      <c r="I35" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J35" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K35" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L35" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M35" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N35" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="O35" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="P35" s="64" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q35" s="67" t="s">
-        <v>248</v>
-      </c>
-      <c r="R35" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="59"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="54"/>
       <c r="S35" s="34"/>
-      <c r="T35" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U35" s="34">
-        <v>2</v>
-      </c>
+      <c r="T35" s="82"/>
+      <c r="U35" s="34"/>
     </row>
     <row r="36" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>22</v>
       </c>
-      <c r="B36" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="C36" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="D36" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="53" t="s">
-        <v>78</v>
-      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
       <c r="F36" s="53"/>
-      <c r="G36" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" s="53">
-        <v>21</v>
-      </c>
-      <c r="I36" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J36" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K36" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L36" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M36" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N36" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O36" s="84" t="s">
-        <v>62</v>
-      </c>
-      <c r="P36" s="80" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q36" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="R36" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="84"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="54"/>
       <c r="S36" s="34"/>
-      <c r="T36" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U36" s="34">
-        <v>2</v>
-      </c>
+      <c r="T36" s="82"/>
+      <c r="U36" s="34"/>
     </row>
     <row r="37" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>23</v>
       </c>
-      <c r="B37" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="C37" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" s="53" t="s">
-        <v>65</v>
-      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
       <c r="F37" s="53"/>
-      <c r="G37" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="53">
-        <v>22</v>
-      </c>
-      <c r="I37" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J37" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K37" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L37" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M37" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N37" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O37" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P37" s="68" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q37" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="R37" s="54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="68"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="54"/>
       <c r="S37" s="34"/>
-      <c r="T37" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="U37" s="34">
-        <v>2</v>
-      </c>
+      <c r="T37" s="82"/>
+      <c r="U37" s="34"/>
     </row>
     <row r="38" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>24</v>
       </c>
-      <c r="B38" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="C38" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="E38" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="F38" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="G38" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" s="53">
-        <v>22</v>
-      </c>
-      <c r="I38" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J38" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K38" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L38" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M38" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N38" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O38" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="P38" s="65" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q38" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="R38" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="53"/>
       <c r="S38" s="23"/>
-      <c r="T38" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U38" s="34">
-        <v>2</v>
-      </c>
+      <c r="T38" s="54"/>
+      <c r="U38" s="34"/>
     </row>
     <row r="39" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>25</v>
       </c>
-      <c r="B39" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C39" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="G39" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H39" s="53">
-        <v>37</v>
-      </c>
-      <c r="I39" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J39" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K39" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L39" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M39" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N39" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O39" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="P39" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q39" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="R39" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="59"/>
+      <c r="N39" s="53"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="53"/>
       <c r="S39" s="54"/>
-      <c r="T39" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U39" s="34">
-        <v>2</v>
-      </c>
+      <c r="T39" s="54"/>
+      <c r="U39" s="34"/>
     </row>
     <row r="40" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>26</v>
       </c>
-      <c r="B40" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="C40" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="E40" s="53" t="s">
-        <v>64</v>
-      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
       <c r="F40" s="53"/>
-      <c r="G40" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H40" s="53">
-        <v>21</v>
-      </c>
-      <c r="I40" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J40" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K40" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L40" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M40" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N40" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O40" s="65" t="s">
-        <v>62</v>
-      </c>
-      <c r="P40" s="68" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q40" s="67" t="s">
-        <v>181</v>
-      </c>
-      <c r="R40" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="59"/>
+      <c r="N40" s="53"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="68"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="53"/>
       <c r="S40" s="54"/>
-      <c r="T40" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U40" s="34">
-        <v>2</v>
-      </c>
+      <c r="T40" s="54"/>
+      <c r="U40" s="34"/>
     </row>
     <row r="41" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>27</v>
       </c>
-      <c r="B41" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="C41" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="53" t="s">
-        <v>156</v>
-      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
       <c r="F41" s="53"/>
-      <c r="G41" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H41" s="53">
-        <v>22</v>
-      </c>
-      <c r="I41" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J41" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K41" s="59" t="s">
-        <v>173</v>
-      </c>
-      <c r="L41" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M41" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N41" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O41" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="P41" s="85" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q41" s="67" t="s">
-        <v>175</v>
-      </c>
-      <c r="R41" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="53"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="53"/>
       <c r="S41" s="54"/>
-      <c r="T41" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U41" s="34">
-        <v>2</v>
-      </c>
+      <c r="T41" s="54"/>
+      <c r="U41" s="34"/>
     </row>
     <row r="42" spans="1:21" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>28</v>
       </c>
-      <c r="B42" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="C42" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="D42" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="E42" s="53" t="s">
-        <v>84</v>
-      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
       <c r="F42" s="53"/>
-      <c r="G42" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H42" s="53">
-        <v>25</v>
-      </c>
-      <c r="I42" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K42" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="L42" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="M42" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="N42" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="O42" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="P42" s="64" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q42" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="R42" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="G42" s="53"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="59"/>
+      <c r="L42" s="53"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="53"/>
+      <c r="O42" s="61"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="53"/>
       <c r="S42" s="54"/>
-      <c r="T42" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U42" s="34">
-        <v>2</v>
-      </c>
+      <c r="T42" s="54"/>
+      <c r="U42" s="34"/>
     </row>
     <row r="43" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>29</v>
       </c>
-      <c r="B43" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="C43" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="D43" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="G43" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H43" s="53">
-        <v>36</v>
-      </c>
-      <c r="I43" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="J43" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="K43" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="L43" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="M43" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="N43" s="53">
-        <v>300</v>
-      </c>
-      <c r="O43" s="61" t="s">
-        <v>255</v>
-      </c>
-      <c r="P43" s="69" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q43" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="R43" s="53" t="s">
-        <v>62</v>
-      </c>
+      <c r="B43" s="22"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="59"/>
+      <c r="K43" s="59"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="59"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="61"/>
+      <c r="P43" s="69"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="53"/>
       <c r="S43" s="54"/>
-      <c r="T43" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U43" s="34">
-        <v>2</v>
-      </c>
+      <c r="T43" s="54"/>
+      <c r="U43" s="34"/>
     </row>
     <row r="44" spans="1:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>30</v>
       </c>
-      <c r="B44" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="C44" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D44" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" s="53" t="s">
-        <v>163</v>
-      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
       <c r="F44" s="53"/>
-      <c r="G44" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="53">
-        <v>23</v>
-      </c>
-      <c r="I44" s="59" t="s">
-        <v>164</v>
-      </c>
-      <c r="J44" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="K44" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="L44" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="M44" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="N44" s="53">
-        <v>8</v>
-      </c>
-      <c r="O44" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="P44" s="63" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q44" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="R44" s="53" t="s">
-        <v>170</v>
-      </c>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="62"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="53"/>
       <c r="S44" s="54"/>
-      <c r="T44" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="U44" s="34">
-        <v>2</v>
-      </c>
+      <c r="T44" s="54"/>
+      <c r="U44" s="34"/>
     </row>
     <row r="45" spans="1:21" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
@@ -4475,14 +2796,12 @@
       <c r="B69" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C69" s="60" t="s">
-        <v>69</v>
-      </c>
+      <c r="C69" s="60"/>
     </row>
     <row r="70" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="52"/>
       <c r="C70" s="41" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4491,15 +2810,13 @@
     </row>
     <row r="72" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="60" t="s">
-        <v>70</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C72" s="60"/>
     </row>
     <row r="73" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C73" s="41" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5442,34 +3759,9 @@
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="B5:H8"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="O15" r:id="rId1" display="abccompany@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="O20" r:id="rId2" display="joan20.pmi@gmail.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="O21" r:id="rId3" display="mjmangabat@filoillogistics.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="O22" r:id="rId4" display="stellargrounds2016@gmail.com" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="O23" r:id="rId5" display="ropalipuerto01@gmail.com" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O27" r:id="rId6" display="jamescarlo.goh@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="O29" r:id="rId7" display="dh.taytaypalawan@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="O25" r:id="rId8" display="mk.aborlan@mitsukoshi.com" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O26" r:id="rId9" display="hrd@opascor.com" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="O30" r:id="rId10" display="mk.narra@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="O31" r:id="rId11" display="mitsukoshimotors@gmail.com" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="P36" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="O36" r:id="rId13" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O37" r:id="rId14" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="O38" r:id="rId15" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="O39" r:id="rId16" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="O41" r:id="rId17" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="O42" r:id="rId18" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="O43" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="P44" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="O44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="O28" r:id="rId22" display="dh.taytaypalawan@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="O33" r:id="rId23" display="avelyn.alcantara@mitsukoshimotors.com" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup scale="55" fitToWidth="0" orientation="landscape" r:id="rId24"/>
-  <drawing r:id="rId25"/>
+  <pageSetup scale="55" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5498,7 +3790,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B1" s="103"/>
       <c r="C1" s="103"/>
@@ -5545,7 +3837,7 @@
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="107" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="108"/>
       <c r="C4" s="108"/>
@@ -5593,7 +3885,7 @@
     <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="109" t="s">
         <v>2</v>
@@ -5611,11 +3903,9 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>76</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C9" s="109"/>
       <c r="D9" s="109"/>
       <c r="E9" s="109"/>
       <c r="F9" s="109"/>
@@ -5629,11 +3919,9 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="110" t="s">
-        <v>258</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C10" s="110"/>
       <c r="D10" s="110"/>
       <c r="E10" s="110"/>
       <c r="F10" s="110"/>
@@ -5659,28 +3947,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="104" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="E12" s="106" t="s">
         <v>38</v>
-      </c>
-      <c r="D12" s="104" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="106" t="s">
-        <v>40</v>
       </c>
       <c r="F12" s="105"/>
       <c r="G12" s="105"/>
       <c r="H12" s="105"/>
       <c r="I12" s="104" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J12" s="105"/>
       <c r="K12" s="105"/>
       <c r="L12" s="105"/>
       <c r="M12" s="106" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="31" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5689,10 +3977,10 @@
       <c r="C13" s="105"/>
       <c r="D13" s="105"/>
       <c r="E13" s="32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" s="33" t="s">
         <v>27</v>
@@ -5701,16 +3989,16 @@
         <v>14</v>
       </c>
       <c r="I13" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="L13" s="33" t="s">
         <v>46</v>
-      </c>
-      <c r="K13" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="L13" s="33" t="s">
-        <v>48</v>
       </c>
       <c r="M13" s="105"/>
     </row>
@@ -5718,83 +4006,35 @@
       <c r="A14" s="9">
         <v>1</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="28">
-        <v>1</v>
-      </c>
-      <c r="E14" s="28">
-        <v>19</v>
-      </c>
-      <c r="F14" s="28">
-        <v>12</v>
-      </c>
-      <c r="G14" s="28">
-        <v>7</v>
-      </c>
-      <c r="H14" s="28">
-        <v>5</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>58</v>
-      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="D15" s="25">
-        <v>2</v>
-      </c>
-      <c r="E15" s="25">
-        <v>30</v>
-      </c>
-      <c r="F15" s="25">
-        <v>15</v>
-      </c>
-      <c r="G15" s="25">
-        <v>15</v>
-      </c>
-      <c r="H15" s="25">
-        <v>2</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="M15" s="25" t="s">
-        <v>58</v>
-      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
@@ -7591,7 +5831,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="111" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -7650,7 +5890,7 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="112"/>
       <c r="D5" s="113"/>
@@ -7658,7 +5898,7 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="112"/>
       <c r="D6" s="113"/>
@@ -7666,7 +5906,7 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="112"/>
       <c r="D7" s="113"/>
@@ -7678,16 +5918,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>10</v>
@@ -7696,31 +5936,31 @@
         <v>12</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="K9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
